--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -121,10 +121,42 @@
     <t xml:space="preserve">(ИИН, наименование и адрес)</t>
   </si>
   <si>
-    <t xml:space="preserve">Грузополучатель: {organization.organization}</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">Грузополучатель: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>{organization.organization}</t>
+    </r>
   </si>
   <si>
-    <t xml:space="preserve">БИН и адрес места нахождения получателя: БИН:{organization.bin}, {organization.address}</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">БИН и адрес места нахождения получателя: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">БИН:{organization.bin}, {organization.address}</t>
+    </r>
   </si>
   <si>
     <r>
@@ -143,7 +175,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК:{organization.bik} КБЕ: {organization.kbe} КНП: </t>
+      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК:{organization.bik} КБЕ: {organization.kbe} </t>
     </r>
     <r>
       <rPr>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -155,7 +155,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН:{organization.bin}, {organization.address}</t>
+      <t xml:space="preserve">БИН:{organization.bin}, город {organization.city}, {organization.index}, {organization.address}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -175,7 +175,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК:{organization.bik} КБЕ: {organization.kbe} </t>
+      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК:{organization.bik} {organization.kbe} </t>
     </r>
     <r>
       <rPr>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -248,10 +248,10 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
+    <t>{costPerDayFormatted}</t>
   </si>
   <si>
-    <t>{totalPrice}</t>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t xml:space="preserve">без НДС</t>
@@ -276,7 +276,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">  {totalPriceWords}</t>
+      <t xml:space="preserve">  {totalCostRu}</t>
     </r>
     <r>
       <rPr>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -136,7 +136,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>{organization.organization}</t>
+      <t>{customer.organization.organization}</t>
     </r>
   </si>
   <si>
@@ -155,7 +155,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН:{organization.bin}, город {organization.city}, {organization.index}, {organization.address}</t>
+      <t xml:space="preserve">БИН:{customer.organization.bin}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
     </r>
   </si>
   <si>
@@ -175,34 +175,15 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК:{organization.bik} {organization.kbe} </t>
+      <t xml:space="preserve"> {customer.organization.iik}, {customer.organization.bank}, БИК:{customer.organization.bik} {customer.organization.kbe} </t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="false"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>organization.knp</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>}</t>
+      <t>{customer.organization.knp}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -155,7 +155,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН:{customer.organization.bin}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
+      <t xml:space="preserve">БИН:{customer.organization.bin}, город {customer.organization.city}, {customer.organization.index} {customer.organization.address}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -147,7 +147,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН и адрес места нахождения получателя: </t>
+      <t xml:space="preserve">БИН и адрес места нахождения грузополучателя: </t>
     </r>
     <r>
       <rPr>
@@ -166,7 +166,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">ИИК получателя: </t>
+      <t xml:space="preserve">ИИК грузополучателя: </t>
     </r>
     <r>
       <rPr>

--- a/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/Tax Invoice.xlsx
@@ -266,7 +266,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> тенге 00 тиын</t>
+      <t xml:space="preserve"> тенге{totalCostCentsRu} тиын</t>
     </r>
   </si>
   <si>
